--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T20:06:34+00:00</t>
+    <t>2025-01-17T09:25:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T09:25:14+00:00</t>
+    <t>2025-01-17T12:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:03:37+00:00</t>
+    <t>2025-01-20T07:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T07:38:35+00:00</t>
+    <t>2025-01-20T07:50:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-diab-composition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10114" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10152" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T07:50:11+00:00</t>
+    <t>2025-01-21T10:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2099,6 +2099,16 @@
   </si>
   <si>
     <t xml:space="preserve">Reference(CarePlan)
+</t>
+  </si>
+  <si>
+    <t>Composition.section:sectionPlanOfCare.entry:schulungen</t>
+  </si>
+  <si>
+    <t>schulungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://diab.iv.elga.gv.at/StructureDefinition/iv-careplan-schulung)
 </t>
   </si>
   <si>
@@ -2620,7 +2630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO270"/>
+  <dimension ref="A1:AO271"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="74.60546875" customWidth="true" bestFit="true"/>
@@ -28665,9 +28675,11 @@
         <v>657</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C222" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C222" t="s" s="2">
+        <v>658</v>
+      </c>
       <c r="D222" t="s" s="2">
         <v>20</v>
       </c>
@@ -28676,7 +28688,7 @@
         <v>78</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>20</v>
@@ -28688,20 +28700,18 @@
         <v>20</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>170</v>
+        <v>659</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O222" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
         <v>20</v>
       </c>
@@ -28725,13 +28735,13 @@
         <v>20</v>
       </c>
       <c r="X222" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Y222" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="Z222" t="s" s="2">
-        <v>424</v>
+        <v>20</v>
       </c>
       <c r="AA222" t="s" s="2">
         <v>20</v>
@@ -28749,13 +28759,13 @@
         <v>20</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI222" t="s" s="2">
         <v>415</v>
@@ -28767,10 +28777,10 @@
         <v>20</v>
       </c>
       <c r="AL222" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>166</v>
+        <v>417</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>20</v>
@@ -28781,10 +28791,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -28795,7 +28805,7 @@
         <v>78</v>
       </c>
       <c r="G223" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H223" t="s" s="2">
         <v>20</v>
@@ -28807,18 +28817,20 @@
         <v>20</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O223" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="O223" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P223" t="s" s="2">
         <v>20</v>
       </c>
@@ -28842,13 +28854,13 @@
         <v>20</v>
       </c>
       <c r="X223" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>20</v>
@@ -28866,16 +28878,16 @@
         <v>20</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH223" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="AJ223" t="s" s="2">
         <v>101</v>
@@ -28884,10 +28896,10 @@
         <v>20</v>
       </c>
       <c r="AL223" t="s" s="2">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>430</v>
+        <v>166</v>
       </c>
       <c r="AN223" t="s" s="2">
         <v>20</v>
@@ -28898,14 +28910,12 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C224" t="s" s="2">
-        <v>660</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
         <v>20</v>
       </c>
@@ -28914,7 +28924,7 @@
         <v>78</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>20</v>
@@ -28926,15 +28936,17 @@
         <v>20</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>358</v>
+        <v>427</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N224" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N224" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
         <v>20</v>
@@ -28983,7 +28995,7 @@
         <v>20</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>356</v>
+        <v>426</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>78</v>
@@ -28992,10 +29004,10 @@
         <v>79</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>362</v>
+        <v>101</v>
       </c>
       <c r="AK224" t="s" s="2">
         <v>20</v>
@@ -29004,7 +29016,7 @@
         <v>363</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>364</v>
+        <v>430</v>
       </c>
       <c r="AN224" t="s" s="2">
         <v>20</v>
@@ -29015,12 +29027,14 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C225" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C225" t="s" s="2">
+        <v>663</v>
+      </c>
       <c r="D225" t="s" s="2">
         <v>20</v>
       </c>
@@ -29041,13 +29055,13 @@
         <v>20</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>260</v>
+        <v>358</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>261</v>
+        <v>359</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29098,28 +29112,28 @@
         <v>20</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>262</v>
+        <v>356</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI225" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ225" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="AK225" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>166</v>
+        <v>363</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>20</v>
@@ -29130,21 +29144,21 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G226" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H226" t="s" s="2">
         <v>20</v>
@@ -29156,17 +29170,15 @@
         <v>20</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N226" s="2"/>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>20</v>
@@ -29215,19 +29227,19 @@
         <v>20</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH226" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI226" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK226" t="s" s="2">
         <v>20</v>
@@ -29247,14 +29259,14 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
@@ -29267,26 +29279,24 @@
         <v>20</v>
       </c>
       <c r="I227" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K227" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="N227" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O227" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
         <v>20</v>
       </c>
@@ -29334,7 +29344,7 @@
         <v>20</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>78</v>
@@ -29352,7 +29362,7 @@
         <v>20</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>20</v>
@@ -29366,45 +29376,45 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>369</v>
+        <v>267</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I228" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J228" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>370</v>
+        <v>268</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>372</v>
+        <v>138</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>20</v>
@@ -29453,28 +29463,28 @@
         <v>20</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK228" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="AM228" t="s" s="2">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="AN228" t="s" s="2">
         <v>20</v>
@@ -29485,18 +29495,18 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G229" t="s" s="2">
         <v>89</v>
@@ -29511,19 +29521,19 @@
         <v>20</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>20</v>
@@ -29533,7 +29543,7 @@
         <v>20</v>
       </c>
       <c r="S229" t="s" s="2">
-        <v>666</v>
+        <v>20</v>
       </c>
       <c r="T229" t="s" s="2">
         <v>20</v>
@@ -29548,13 +29558,13 @@
         <v>20</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>20</v>
@@ -29572,7 +29582,7 @@
         <v>20</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>78</v>
@@ -29590,10 +29600,10 @@
         <v>20</v>
       </c>
       <c r="AL229" t="s" s="2">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="AM229" t="s" s="2">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="AN229" t="s" s="2">
         <v>20</v>
@@ -29604,10 +29614,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29615,10 +29625,10 @@
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>20</v>
@@ -29630,17 +29640,19 @@
         <v>20</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N230" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N230" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O230" t="s" s="2">
-        <v>228</v>
+        <v>378</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>20</v>
@@ -29650,7 +29662,7 @@
         <v>20</v>
       </c>
       <c r="S230" t="s" s="2">
-        <v>20</v>
+        <v>669</v>
       </c>
       <c r="T230" t="s" s="2">
         <v>20</v>
@@ -29665,13 +29677,13 @@
         <v>20</v>
       </c>
       <c r="X230" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="Y230" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="Z230" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>20</v>
@@ -29689,13 +29701,13 @@
         <v>20</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>20</v>
@@ -29707,24 +29719,24 @@
         <v>20</v>
       </c>
       <c r="AL230" t="s" s="2">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="AM230" t="s" s="2">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="AN230" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -29735,7 +29747,7 @@
         <v>78</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>20</v>
@@ -29747,18 +29759,18 @@
         <v>20</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>352</v>
+        <v>225</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O231" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N231" s="2"/>
+      <c r="O231" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P231" t="s" s="2">
         <v>20</v>
       </c>
@@ -29806,13 +29818,13 @@
         <v>20</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI231" t="s" s="2">
         <v>20</v>
@@ -29824,24 +29836,24 @@
         <v>20</v>
       </c>
       <c r="AL231" t="s" s="2">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>388</v>
+        <v>231</v>
       </c>
       <c r="AN231" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -29864,16 +29876,16 @@
         <v>20</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>119</v>
+        <v>352</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -29923,7 +29935,7 @@
         <v>20</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>78</v>
@@ -29932,7 +29944,7 @@
         <v>89</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>101</v>
@@ -29941,10 +29953,10 @@
         <v>20</v>
       </c>
       <c r="AL232" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="AM232" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AN232" t="s" s="2">
         <v>20</v>
@@ -29955,10 +29967,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -29981,20 +29993,18 @@
         <v>20</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O233" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
         <v>20</v>
       </c>
@@ -30018,13 +30028,13 @@
         <v>20</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>20</v>
@@ -30042,7 +30052,7 @@
         <v>20</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>78</v>
@@ -30051,7 +30061,7 @@
         <v>89</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AJ233" t="s" s="2">
         <v>101</v>
@@ -30060,24 +30070,24 @@
         <v>20</v>
       </c>
       <c r="AL233" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="AM233" t="s" s="2">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="AN233" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30100,19 +30110,19 @@
         <v>20</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>20</v>
@@ -30137,13 +30147,13 @@
         <v>20</v>
       </c>
       <c r="X234" t="s" s="2">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="Y234" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="Z234" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>20</v>
@@ -30161,7 +30171,7 @@
         <v>20</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>78</v>
@@ -30179,7 +30189,7 @@
         <v>20</v>
       </c>
       <c r="AL234" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="AM234" t="s" s="2">
         <v>166</v>
@@ -30188,15 +30198,15 @@
         <v>20</v>
       </c>
       <c r="AO234" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30207,7 +30217,7 @@
         <v>78</v>
       </c>
       <c r="G235" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H235" t="s" s="2">
         <v>20</v>
@@ -30219,18 +30229,20 @@
         <v>20</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>593</v>
+        <v>170</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O235" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="O235" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P235" t="s" s="2">
         <v>20</v>
       </c>
@@ -30254,38 +30266,40 @@
         <v>20</v>
       </c>
       <c r="X235" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y235" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="Z235" t="s" s="2">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="AA235" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB235" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AC235" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC235" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD235" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE235" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH235" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>415</v>
+        <v>20</v>
       </c>
       <c r="AJ235" t="s" s="2">
         <v>101</v>
@@ -30294,10 +30308,10 @@
         <v>20</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="AM235" t="s" s="2">
-        <v>417</v>
+        <v>166</v>
       </c>
       <c r="AN235" t="s" s="2">
         <v>20</v>
@@ -30308,14 +30322,12 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="C236" t="s" s="2">
-        <v>674</v>
-      </c>
+      <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
         <v>20</v>
       </c>
@@ -30324,7 +30336,7 @@
         <v>78</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>20</v>
@@ -30336,7 +30348,7 @@
         <v>20</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>675</v>
+        <v>593</v>
       </c>
       <c r="L236" t="s" s="2">
         <v>412</v>
@@ -30383,16 +30395,14 @@
         <v>20</v>
       </c>
       <c r="AB236" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="AC236" s="2"/>
       <c r="AD236" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE236" t="s" s="2">
-        <v>20</v>
+        <v>361</v>
       </c>
       <c r="AF236" t="s" s="2">
         <v>411</v>
@@ -30549,9 +30559,11 @@
         <v>679</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C238" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C238" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="D238" t="s" s="2">
         <v>20</v>
       </c>
@@ -30572,20 +30584,18 @@
         <v>20</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>170</v>
+        <v>681</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="N238" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O238" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
         <v>20</v>
       </c>
@@ -30609,13 +30619,13 @@
         <v>20</v>
       </c>
       <c r="X238" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Y238" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="Z238" t="s" s="2">
-        <v>424</v>
+        <v>20</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>20</v>
@@ -30633,13 +30643,13 @@
         <v>20</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI238" t="s" s="2">
         <v>415</v>
@@ -30651,10 +30661,10 @@
         <v>20</v>
       </c>
       <c r="AL238" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="AM238" t="s" s="2">
-        <v>166</v>
+        <v>417</v>
       </c>
       <c r="AN238" t="s" s="2">
         <v>20</v>
@@ -30665,10 +30675,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -30679,7 +30689,7 @@
         <v>78</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H239" t="s" s="2">
         <v>20</v>
@@ -30691,18 +30701,20 @@
         <v>20</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O239" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="O239" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P239" t="s" s="2">
         <v>20</v>
       </c>
@@ -30726,13 +30738,13 @@
         <v>20</v>
       </c>
       <c r="X239" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y239" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="Z239" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>20</v>
@@ -30750,16 +30762,16 @@
         <v>20</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>101</v>
@@ -30768,10 +30780,10 @@
         <v>20</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>430</v>
+        <v>166</v>
       </c>
       <c r="AN239" t="s" s="2">
         <v>20</v>
@@ -30782,14 +30794,12 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C240" t="s" s="2">
-        <v>682</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
         <v>20</v>
       </c>
@@ -30798,7 +30808,7 @@
         <v>78</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>20</v>
@@ -30810,15 +30820,17 @@
         <v>20</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>358</v>
+        <v>427</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N240" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N240" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>20</v>
@@ -30867,7 +30879,7 @@
         <v>20</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>356</v>
+        <v>426</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>78</v>
@@ -30876,10 +30888,10 @@
         <v>79</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AJ240" t="s" s="2">
-        <v>362</v>
+        <v>101</v>
       </c>
       <c r="AK240" t="s" s="2">
         <v>20</v>
@@ -30888,7 +30900,7 @@
         <v>363</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>364</v>
+        <v>430</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>20</v>
@@ -30899,12 +30911,14 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C241" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C241" t="s" s="2">
+        <v>685</v>
+      </c>
       <c r="D241" t="s" s="2">
         <v>20</v>
       </c>
@@ -30925,13 +30939,13 @@
         <v>20</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>260</v>
+        <v>358</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>261</v>
+        <v>359</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -30982,28 +30996,28 @@
         <v>20</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>262</v>
+        <v>356</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH241" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI241" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ241" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="AK241" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>166</v>
+        <v>363</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="AN241" t="s" s="2">
         <v>20</v>
@@ -31014,21 +31028,21 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G242" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H242" t="s" s="2">
         <v>20</v>
@@ -31040,17 +31054,15 @@
         <v>20</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N242" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N242" s="2"/>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
         <v>20</v>
@@ -31099,19 +31111,19 @@
         <v>20</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH242" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI242" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK242" t="s" s="2">
         <v>20</v>
@@ -31131,14 +31143,14 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
@@ -31151,26 +31163,24 @@
         <v>20</v>
       </c>
       <c r="I243" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J243" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K243" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="N243" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O243" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
         <v>20</v>
       </c>
@@ -31218,7 +31228,7 @@
         <v>20</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>78</v>
@@ -31236,7 +31246,7 @@
         <v>20</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="AM243" t="s" s="2">
         <v>20</v>
@@ -31250,45 +31260,45 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
-        <v>369</v>
+        <v>267</v>
       </c>
       <c r="E244" s="2"/>
       <c r="F244" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I244" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J244" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>370</v>
+        <v>268</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>372</v>
+        <v>138</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>20</v>
@@ -31337,28 +31347,28 @@
         <v>20</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK244" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="AM244" t="s" s="2">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="AN244" t="s" s="2">
         <v>20</v>
@@ -31369,18 +31379,18 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G245" t="s" s="2">
         <v>89</v>
@@ -31395,19 +31405,19 @@
         <v>20</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="O245" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>20</v>
@@ -31417,7 +31427,7 @@
         <v>20</v>
       </c>
       <c r="S245" t="s" s="2">
-        <v>688</v>
+        <v>20</v>
       </c>
       <c r="T245" t="s" s="2">
         <v>20</v>
@@ -31432,13 +31442,13 @@
         <v>20</v>
       </c>
       <c r="X245" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="Y245" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Z245" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>20</v>
@@ -31456,7 +31466,7 @@
         <v>20</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>78</v>
@@ -31474,10 +31484,10 @@
         <v>20</v>
       </c>
       <c r="AL245" t="s" s="2">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="AM245" t="s" s="2">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="AN245" t="s" s="2">
         <v>20</v>
@@ -31488,10 +31498,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31499,10 +31509,10 @@
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G246" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H246" t="s" s="2">
         <v>20</v>
@@ -31514,17 +31524,19 @@
         <v>20</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N246" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N246" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O246" t="s" s="2">
-        <v>228</v>
+        <v>378</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>20</v>
@@ -31534,7 +31546,7 @@
         <v>20</v>
       </c>
       <c r="S246" t="s" s="2">
-        <v>20</v>
+        <v>691</v>
       </c>
       <c r="T246" t="s" s="2">
         <v>20</v>
@@ -31549,13 +31561,13 @@
         <v>20</v>
       </c>
       <c r="X246" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="Y246" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="Z246" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>20</v>
@@ -31573,13 +31585,13 @@
         <v>20</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH246" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI246" t="s" s="2">
         <v>20</v>
@@ -31591,24 +31603,24 @@
         <v>20</v>
       </c>
       <c r="AL246" t="s" s="2">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="AM246" t="s" s="2">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="AN246" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO246" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -31619,7 +31631,7 @@
         <v>78</v>
       </c>
       <c r="G247" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H247" t="s" s="2">
         <v>20</v>
@@ -31631,18 +31643,18 @@
         <v>20</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>352</v>
+        <v>225</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N247" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O247" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N247" s="2"/>
+      <c r="O247" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P247" t="s" s="2">
         <v>20</v>
       </c>
@@ -31690,13 +31702,13 @@
         <v>20</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH247" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI247" t="s" s="2">
         <v>20</v>
@@ -31708,24 +31720,24 @@
         <v>20</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="AM247" t="s" s="2">
-        <v>388</v>
+        <v>231</v>
       </c>
       <c r="AN247" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO247" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -31748,16 +31760,16 @@
         <v>20</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>119</v>
+        <v>352</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="N248" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="O248" s="2"/>
       <c r="P248" t="s" s="2">
@@ -31807,7 +31819,7 @@
         <v>20</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>78</v>
@@ -31816,7 +31828,7 @@
         <v>89</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>101</v>
@@ -31825,10 +31837,10 @@
         <v>20</v>
       </c>
       <c r="AL248" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="AM248" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AN248" t="s" s="2">
         <v>20</v>
@@ -31839,10 +31851,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -31865,20 +31877,18 @@
         <v>20</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="N249" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O249" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="O249" s="2"/>
       <c r="P249" t="s" s="2">
         <v>20</v>
       </c>
@@ -31902,13 +31912,13 @@
         <v>20</v>
       </c>
       <c r="X249" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="Y249" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="Z249" t="s" s="2">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="AA249" t="s" s="2">
         <v>20</v>
@@ -31926,7 +31936,7 @@
         <v>20</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>78</v>
@@ -31935,7 +31945,7 @@
         <v>89</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>101</v>
@@ -31944,24 +31954,24 @@
         <v>20</v>
       </c>
       <c r="AL249" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="AM249" t="s" s="2">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="AN249" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO249" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -31984,19 +31994,19 @@
         <v>20</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="N250" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="O250" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>20</v>
@@ -32021,13 +32031,13 @@
         <v>20</v>
       </c>
       <c r="X250" t="s" s="2">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="Y250" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="Z250" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="AA250" t="s" s="2">
         <v>20</v>
@@ -32045,7 +32055,7 @@
         <v>20</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>78</v>
@@ -32063,7 +32073,7 @@
         <v>20</v>
       </c>
       <c r="AL250" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="AM250" t="s" s="2">
         <v>166</v>
@@ -32072,15 +32082,15 @@
         <v>20</v>
       </c>
       <c r="AO250" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32091,7 +32101,7 @@
         <v>78</v>
       </c>
       <c r="G251" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H251" t="s" s="2">
         <v>20</v>
@@ -32103,18 +32113,20 @@
         <v>20</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>593</v>
+        <v>170</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O251" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="O251" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P251" t="s" s="2">
         <v>20</v>
       </c>
@@ -32138,38 +32150,40 @@
         <v>20</v>
       </c>
       <c r="X251" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y251" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="Z251" t="s" s="2">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB251" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AC251" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC251" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD251" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE251" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH251" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI251" t="s" s="2">
-        <v>415</v>
+        <v>20</v>
       </c>
       <c r="AJ251" t="s" s="2">
         <v>101</v>
@@ -32178,10 +32192,10 @@
         <v>20</v>
       </c>
       <c r="AL251" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>417</v>
+        <v>166</v>
       </c>
       <c r="AN251" t="s" s="2">
         <v>20</v>
@@ -32192,14 +32206,12 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="C252" t="s" s="2">
-        <v>696</v>
-      </c>
+      <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
         <v>20</v>
       </c>
@@ -32220,7 +32232,7 @@
         <v>20</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>697</v>
+        <v>593</v>
       </c>
       <c r="L252" t="s" s="2">
         <v>412</v>
@@ -32267,16 +32279,14 @@
         <v>20</v>
       </c>
       <c r="AB252" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC252" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="AC252" s="2"/>
       <c r="AD252" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE252" t="s" s="2">
-        <v>20</v>
+        <v>361</v>
       </c>
       <c r="AF252" t="s" s="2">
         <v>411</v>
@@ -32433,9 +32443,11 @@
         <v>701</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C254" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C254" t="s" s="2">
+        <v>702</v>
+      </c>
       <c r="D254" t="s" s="2">
         <v>20</v>
       </c>
@@ -32444,7 +32456,7 @@
         <v>78</v>
       </c>
       <c r="G254" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H254" t="s" s="2">
         <v>20</v>
@@ -32456,20 +32468,18 @@
         <v>20</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>170</v>
+        <v>703</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="N254" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O254" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="O254" s="2"/>
       <c r="P254" t="s" s="2">
         <v>20</v>
       </c>
@@ -32493,13 +32503,13 @@
         <v>20</v>
       </c>
       <c r="X254" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Y254" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="Z254" t="s" s="2">
-        <v>424</v>
+        <v>20</v>
       </c>
       <c r="AA254" t="s" s="2">
         <v>20</v>
@@ -32517,13 +32527,13 @@
         <v>20</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI254" t="s" s="2">
         <v>415</v>
@@ -32535,10 +32545,10 @@
         <v>20</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="AM254" t="s" s="2">
-        <v>166</v>
+        <v>417</v>
       </c>
       <c r="AN254" t="s" s="2">
         <v>20</v>
@@ -32549,10 +32559,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -32563,7 +32573,7 @@
         <v>78</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H255" t="s" s="2">
         <v>20</v>
@@ -32575,18 +32585,20 @@
         <v>20</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="N255" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O255" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="O255" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P255" t="s" s="2">
         <v>20</v>
       </c>
@@ -32610,13 +32622,13 @@
         <v>20</v>
       </c>
       <c r="X255" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y255" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="Z255" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>20</v>
@@ -32634,16 +32646,16 @@
         <v>20</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH255" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="AJ255" t="s" s="2">
         <v>101</v>
@@ -32652,10 +32664,10 @@
         <v>20</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="AM255" t="s" s="2">
-        <v>430</v>
+        <v>166</v>
       </c>
       <c r="AN255" t="s" s="2">
         <v>20</v>
@@ -32666,14 +32678,12 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C256" t="s" s="2">
-        <v>704</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
         <v>20</v>
       </c>
@@ -32682,7 +32692,7 @@
         <v>78</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>20</v>
@@ -32694,15 +32704,17 @@
         <v>20</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>358</v>
+        <v>427</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N256" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N256" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
         <v>20</v>
@@ -32751,7 +32763,7 @@
         <v>20</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>356</v>
+        <v>426</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>78</v>
@@ -32760,10 +32772,10 @@
         <v>79</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>362</v>
+        <v>101</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>20</v>
@@ -32772,7 +32784,7 @@
         <v>363</v>
       </c>
       <c r="AM256" t="s" s="2">
-        <v>364</v>
+        <v>430</v>
       </c>
       <c r="AN256" t="s" s="2">
         <v>20</v>
@@ -32783,12 +32795,14 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C257" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C257" t="s" s="2">
+        <v>707</v>
+      </c>
       <c r="D257" t="s" s="2">
         <v>20</v>
       </c>
@@ -32809,13 +32823,13 @@
         <v>20</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>260</v>
+        <v>358</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>261</v>
+        <v>359</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
@@ -32866,28 +32880,28 @@
         <v>20</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>262</v>
+        <v>356</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI257" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="AK257" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>166</v>
+        <v>363</v>
       </c>
       <c r="AM257" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="AN257" t="s" s="2">
         <v>20</v>
@@ -32898,21 +32912,21 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G258" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H258" t="s" s="2">
         <v>20</v>
@@ -32924,17 +32938,15 @@
         <v>20</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N258" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N258" s="2"/>
       <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>20</v>
@@ -32983,19 +32995,19 @@
         <v>20</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH258" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI258" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ258" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK258" t="s" s="2">
         <v>20</v>
@@ -33015,14 +33027,14 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" t="s" s="2">
@@ -33035,26 +33047,24 @@
         <v>20</v>
       </c>
       <c r="I259" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J259" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K259" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="N259" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O259" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O259" s="2"/>
       <c r="P259" t="s" s="2">
         <v>20</v>
       </c>
@@ -33102,7 +33112,7 @@
         <v>20</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>78</v>
@@ -33120,7 +33130,7 @@
         <v>20</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="AM259" t="s" s="2">
         <v>20</v>
@@ -33134,45 +33144,45 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
-        <v>369</v>
+        <v>267</v>
       </c>
       <c r="E260" s="2"/>
       <c r="F260" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G260" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H260" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I260" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J260" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>370</v>
+        <v>268</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="N260" t="s" s="2">
-        <v>372</v>
+        <v>138</v>
       </c>
       <c r="O260" t="s" s="2">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="P260" t="s" s="2">
         <v>20</v>
@@ -33221,28 +33231,28 @@
         <v>20</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH260" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI260" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ260" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK260" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL260" t="s" s="2">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>20</v>
@@ -33253,18 +33263,18 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="E261" s="2"/>
       <c r="F261" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G261" t="s" s="2">
         <v>89</v>
@@ -33279,19 +33289,19 @@
         <v>20</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="N261" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="O261" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="P261" t="s" s="2">
         <v>20</v>
@@ -33301,7 +33311,7 @@
         <v>20</v>
       </c>
       <c r="S261" t="s" s="2">
-        <v>710</v>
+        <v>20</v>
       </c>
       <c r="T261" t="s" s="2">
         <v>20</v>
@@ -33316,13 +33326,13 @@
         <v>20</v>
       </c>
       <c r="X261" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="Y261" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Z261" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AA261" t="s" s="2">
         <v>20</v>
@@ -33340,7 +33350,7 @@
         <v>20</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>78</v>
@@ -33358,10 +33368,10 @@
         <v>20</v>
       </c>
       <c r="AL261" t="s" s="2">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>20</v>
@@ -33372,10 +33382,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33383,10 +33393,10 @@
       </c>
       <c r="E262" s="2"/>
       <c r="F262" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G262" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H262" t="s" s="2">
         <v>20</v>
@@ -33398,17 +33408,19 @@
         <v>20</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N262" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N262" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O262" t="s" s="2">
-        <v>228</v>
+        <v>378</v>
       </c>
       <c r="P262" t="s" s="2">
         <v>20</v>
@@ -33418,7 +33430,7 @@
         <v>20</v>
       </c>
       <c r="S262" t="s" s="2">
-        <v>20</v>
+        <v>713</v>
       </c>
       <c r="T262" t="s" s="2">
         <v>20</v>
@@ -33433,13 +33445,13 @@
         <v>20</v>
       </c>
       <c r="X262" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="Y262" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="Z262" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="AA262" t="s" s="2">
         <v>20</v>
@@ -33457,13 +33469,13 @@
         <v>20</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH262" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI262" t="s" s="2">
         <v>20</v>
@@ -33475,24 +33487,24 @@
         <v>20</v>
       </c>
       <c r="AL262" t="s" s="2">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="AM262" t="s" s="2">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="AN262" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO262" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33503,7 +33515,7 @@
         <v>78</v>
       </c>
       <c r="G263" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H263" t="s" s="2">
         <v>20</v>
@@ -33515,18 +33527,18 @@
         <v>20</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>352</v>
+        <v>225</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N263" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O263" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N263" s="2"/>
+      <c r="O263" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P263" t="s" s="2">
         <v>20</v>
       </c>
@@ -33574,13 +33586,13 @@
         <v>20</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH263" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI263" t="s" s="2">
         <v>20</v>
@@ -33592,24 +33604,24 @@
         <v>20</v>
       </c>
       <c r="AL263" t="s" s="2">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>388</v>
+        <v>231</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO263" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -33632,16 +33644,16 @@
         <v>20</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>119</v>
+        <v>352</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="N264" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
@@ -33691,7 +33703,7 @@
         <v>20</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>78</v>
@@ -33700,7 +33712,7 @@
         <v>89</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="AJ264" t="s" s="2">
         <v>101</v>
@@ -33709,10 +33721,10 @@
         <v>20</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AN264" t="s" s="2">
         <v>20</v>
@@ -33723,10 +33735,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -33749,20 +33761,18 @@
         <v>20</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O265" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="O265" s="2"/>
       <c r="P265" t="s" s="2">
         <v>20</v>
       </c>
@@ -33786,13 +33796,13 @@
         <v>20</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>20</v>
@@ -33810,7 +33820,7 @@
         <v>20</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>78</v>
@@ -33819,7 +33829,7 @@
         <v>89</v>
       </c>
       <c r="AI265" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AJ265" t="s" s="2">
         <v>101</v>
@@ -33828,24 +33838,24 @@
         <v>20</v>
       </c>
       <c r="AL265" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="AM265" t="s" s="2">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="AN265" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO265" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -33868,19 +33878,19 @@
         <v>20</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="O266" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>20</v>
@@ -33905,13 +33915,13 @@
         <v>20</v>
       </c>
       <c r="X266" t="s" s="2">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="Y266" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="Z266" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>20</v>
@@ -33929,7 +33939,7 @@
         <v>20</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>78</v>
@@ -33947,7 +33957,7 @@
         <v>20</v>
       </c>
       <c r="AL266" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="AM266" t="s" s="2">
         <v>166</v>
@@ -33956,15 +33966,15 @@
         <v>20</v>
       </c>
       <c r="AO266" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -33975,7 +33985,7 @@
         <v>78</v>
       </c>
       <c r="G267" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H267" t="s" s="2">
         <v>20</v>
@@ -33987,18 +33997,20 @@
         <v>20</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>717</v>
+        <v>170</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="N267" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O267" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="O267" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P267" t="s" s="2">
         <v>20</v>
       </c>
@@ -34022,38 +34034,40 @@
         <v>20</v>
       </c>
       <c r="X267" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y267" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="Z267" t="s" s="2">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="AA267" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB267" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AC267" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC267" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD267" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE267" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH267" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI267" t="s" s="2">
-        <v>415</v>
+        <v>20</v>
       </c>
       <c r="AJ267" t="s" s="2">
         <v>101</v>
@@ -34062,10 +34076,10 @@
         <v>20</v>
       </c>
       <c r="AL267" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="AM267" t="s" s="2">
-        <v>417</v>
+        <v>166</v>
       </c>
       <c r="AN267" t="s" s="2">
         <v>20</v>
@@ -34076,14 +34090,12 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="C268" t="s" s="2">
-        <v>719</v>
-      </c>
+      <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
         <v>20</v>
       </c>
@@ -34151,16 +34163,14 @@
         <v>20</v>
       </c>
       <c r="AB268" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC268" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="AC268" s="2"/>
       <c r="AD268" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE268" t="s" s="2">
-        <v>20</v>
+        <v>361</v>
       </c>
       <c r="AF268" t="s" s="2">
         <v>411</v>
@@ -34198,9 +34208,11 @@
         <v>721</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C269" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C269" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="D269" t="s" s="2">
         <v>20</v>
       </c>
@@ -34209,7 +34221,7 @@
         <v>78</v>
       </c>
       <c r="G269" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H269" t="s" s="2">
         <v>20</v>
@@ -34221,20 +34233,18 @@
         <v>20</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>170</v>
+        <v>723</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O269" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="O269" s="2"/>
       <c r="P269" t="s" s="2">
         <v>20</v>
       </c>
@@ -34258,13 +34268,13 @@
         <v>20</v>
       </c>
       <c r="X269" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Y269" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="Z269" t="s" s="2">
-        <v>424</v>
+        <v>20</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>20</v>
@@ -34282,13 +34292,13 @@
         <v>20</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH269" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI269" t="s" s="2">
         <v>415</v>
@@ -34300,10 +34310,10 @@
         <v>20</v>
       </c>
       <c r="AL269" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>166</v>
+        <v>417</v>
       </c>
       <c r="AN269" t="s" s="2">
         <v>20</v>
@@ -34314,10 +34324,10 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34328,7 +34338,7 @@
         <v>78</v>
       </c>
       <c r="G270" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H270" t="s" s="2">
         <v>20</v>
@@ -34340,18 +34350,20 @@
         <v>20</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O270" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="O270" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P270" t="s" s="2">
         <v>20</v>
       </c>
@@ -34375,13 +34387,13 @@
         <v>20</v>
       </c>
       <c r="X270" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y270" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="Z270" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AA270" t="s" s="2">
         <v>20</v>
@@ -34399,16 +34411,16 @@
         <v>20</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH270" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI270" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="AJ270" t="s" s="2">
         <v>101</v>
@@ -34417,15 +34429,132 @@
         <v>20</v>
       </c>
       <c r="AL270" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM270" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AN270" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO270" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C271" s="2"/>
+      <c r="D271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E271" s="2"/>
+      <c r="F271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K271" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L271" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M271" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N271" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O271" s="2"/>
+      <c r="P271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q271" s="2"/>
+      <c r="R271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF271" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG271" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI271" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AJ271" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL271" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AM270" t="s" s="2">
+      <c r="AM271" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AN270" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO270" t="s" s="2">
+      <c r="AN271" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO271" t="s" s="2">
         <v>20</v>
       </c>
     </row>
